--- a/data/trans_orig/Q5414-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5414-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de comer solo en 2007</t>
+          <t>Población según si es capaz de comer solo en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4650</t>
+          <t>5422</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55038</t>
+          <t>55061</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27881</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29709</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>84843</t>
+          <t>84071</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48960</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50830</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13918</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15786</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64712</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66616</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5596</t>
+          <t>5993</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>819</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6276</t>
+          <t>7144</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>4282</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1594</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9761</t>
+          <t>8666</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>65478</t>
+          <t>64610</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70959</t>
+          <t>70935</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17599</t>
+          <t>17721</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>85238</t>
+          <t>85910</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>94150</t>
+          <t>94237</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5772</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5716</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>949</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8886</t>
+          <t>8354</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4525</t>
+          <t>4707</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1890</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10449</t>
+          <t>11782</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>247883</t>
+          <t>249010</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>257526</t>
+          <t>258129</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>81227</t>
+          <t>81045</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>332904</t>
+          <t>332337</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>343064</t>
+          <t>343022</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4674</t>
+          <t>4449</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7141</t>
+          <t>7287</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>7942</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>50791</t>
+          <t>51016</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>89109</t>
+          <t>88963</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>143773</t>
+          <t>142392</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>896</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9359</t>
+          <t>9155</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>899</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9046</t>
+          <t>9115</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9759</t>
+          <t>10682</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10699</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>410841</t>
+          <t>409478</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>421872</t>
+          <t>421893</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>413890</t>
+          <t>413740</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>425556</t>
+          <t>425612</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>5668</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10513</t>
+          <t>10434</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>2351</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>12545</t>
+          <t>13351</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15290</t>
+          <t>15383</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4172</t>
+          <t>4264</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>16900</t>
+          <t>15989</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10345</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>27151</t>
+          <t>26577</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>483848</t>
+          <t>484198</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>496205</t>
+          <t>496196</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>655489</t>
+          <t>655807</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>670437</t>
+          <t>669677</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1143846</t>
+          <t>1144301</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1163667</t>
+          <t>1163197</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de comer solo en 2012</t>
+          <t>Población según si es capaz de comer solo en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2151</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2171</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2151</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5978</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5506</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41767</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43918</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19311</t>
+          <t>20488</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>63620</t>
+          <t>63701</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5748</t>
+          <t>4683</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6585</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6234</t>
+          <t>6864</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>4796</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>8994</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54396</t>
+          <t>53766</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12226</t>
+          <t>12624</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>70580</t>
+          <t>69103</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79531</t>
+          <t>78471</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6176</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>5899</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7218</t>
+          <t>6756</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6760</t>
+          <t>7208</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>110033</t>
+          <t>110119</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>117709</t>
+          <t>117712</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>52644</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>54615</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>164208</t>
+          <t>164759</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>172315</t>
+          <t>172342</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>979</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>8432</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>995</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8377</t>
+          <t>8455</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4192</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19493</t>
+          <t>20510</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4270</t>
+          <t>4224</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19753</t>
+          <t>19255</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>208765</t>
+          <t>208900</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>225432</t>
+          <t>225333</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>58112</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>60095</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>269287</t>
+          <t>268659</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>285562</t>
+          <t>285605</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7029</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>12677</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3151</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14826</t>
+          <t>14977</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>6056</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>2978</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13476</t>
+          <t>12771</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14150</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>94328</t>
+          <t>93404</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>101706</t>
+          <t>101696</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>167469</t>
+          <t>167497</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>182928</t>
+          <t>181921</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>266091</t>
+          <t>267474</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>282326</t>
+          <t>282769</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2231</t>
+          <t>2247</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13420</t>
+          <t>13568</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>2188</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>13184</t>
+          <t>13177</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6671</t>
+          <t>6494</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23271</t>
+          <t>22855</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6598</t>
+          <t>6617</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22716</t>
+          <t>22982</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>364219</t>
+          <t>364572</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>382812</t>
+          <t>383818</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>367026</t>
+          <t>366670</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>385545</t>
+          <t>385669</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12429</t>
+          <t>12518</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7820</t>
+          <t>7512</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>22318</t>
+          <t>22651</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11730</t>
+          <t>11830</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>30681</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>7390</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>25110</t>
+          <t>24990</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>13239</t>
+          <t>13341</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>34120</t>
+          <t>33452</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>24654</t>
+          <t>22931</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>51146</t>
+          <t>48628</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>527334</t>
+          <t>528178</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>547274</t>
+          <t>547452</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>693095</t>
+          <t>694868</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>717823</t>
+          <t>718729</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1228184</t>
+          <t>1229841</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1259976</t>
+          <t>1261329</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de comer solo en 2016</t>
+          <t>Población según si es capaz de comer solo en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6426</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>66714</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>68647</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29809</t>
+          <t>29458</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>99109</t>
+          <t>98647</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>5075</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5179</t>
+          <t>4657</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5457</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4428</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47407</t>
+          <t>47274</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15371</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17588</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63802</t>
+          <t>64173</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8615,7 +8615,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3849</t>
+          <t>4566</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -8723,7 +8723,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>116997</t>
+          <t>116936</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43887</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46209</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,7 +8793,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>162621</t>
+          <t>161904</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2232</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>876</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8837</t>
+          <t>9275</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10467</t>
+          <t>10084</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9121,7 +9121,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2521</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13027</t>
+          <t>14116</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>195019</t>
+          <t>194581</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>202971</t>
+          <t>202980</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>88579</t>
+          <t>88962</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>289875</t>
+          <t>288786</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>300381</t>
+          <t>300336</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1741</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7331</t>
+          <t>6706</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6766</t>
+          <t>6834</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>829</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>8734</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9542,7 +9542,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2553</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15286</t>
+          <t>14557</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4749</t>
+          <t>4846</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>17752</t>
+          <t>17998</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>136857</t>
+          <t>136487</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>144394</t>
+          <t>144392</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>142943</t>
+          <t>143493</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>156796</t>
+          <t>156884</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>285059</t>
+          <t>284268</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>299175</t>
+          <t>298951</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3410</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16735</t>
+          <t>17052</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3410</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16735</t>
+          <t>17052</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19267</t>
+          <t>20354</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19267</t>
+          <t>20354</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>383107</t>
+          <t>382028</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>402782</t>
+          <t>401959</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>383107</t>
+          <t>382028</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>402782</t>
+          <t>401959</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,31%</t>
         </is>
       </c>
     </row>
@@ -10326,7 +10326,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19548</t>
+          <t>18066</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4441</t>
+          <t>4609</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>20203</t>
+          <t>19546</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14917</t>
+          <t>15930</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>13543</t>
+          <t>13102</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>34687</t>
+          <t>34090</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>19109</t>
+          <t>20519</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>42941</t>
+          <t>42915</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>575425</t>
+          <t>574837</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>586341</t>
+          <t>586254</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>725412</t>
+          <t>727984</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>751419</t>
+          <t>752320</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1309250</t>
+          <t>1306518</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1335900</t>
+          <t>1334642</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,87%</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10816,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de comer solo en 2023</t>
+          <t>Población según si es capaz de comer solo en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11026,12 +11026,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11061,12 +11061,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11174,12 +11174,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>106379</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>64379</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>171808</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11467,12 +11467,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>2959</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11542,7 +11542,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2802</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -11585,7 +11585,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3074</t>
+          <t>3568</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11600,7 +11600,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91924</t>
+          <t>91430</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -11708,7 +11708,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -11728,7 +11728,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43823</t>
+          <t>43972</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>137705</t>
+          <t>138396</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>2921</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11998,7 +11998,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12013,7 +12013,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>492</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>5661</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12076,7 +12076,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3198</t>
+          <t>3534</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7859</t>
+          <t>7025</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>95396</t>
+          <t>95376</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>101198</t>
+          <t>101093</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49591</t>
+          <t>49255</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>145892</t>
+          <t>146865</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>153314</t>
+          <t>153149</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -12384,7 +12384,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12419,7 +12419,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4637</t>
+          <t>4399</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12434,7 +12434,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12454,7 +12454,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3546</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12469,7 +12469,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2430</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9781</t>
+          <t>9408</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12532,7 +12532,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5553</t>
+          <t>5586</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>1587</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13563</t>
+          <t>12880</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>227857</t>
+          <t>228509</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>235515</t>
+          <t>236012</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>317633</t>
+          <t>317607</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>326502</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>549576</t>
+          <t>549507</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>562521</t>
+          <t>562446</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -12840,7 +12840,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3701</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6772</t>
+          <t>6509</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8119</t>
+          <t>7673</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>389</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>5653</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13312</t>
+          <t>14074</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>6498</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>14615</t>
+          <t>15479</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13038,7 +13038,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>86621</t>
+          <t>86240</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>91241</t>
+          <t>91172</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>187627</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>197297</t>
+          <t>197182</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>277512</t>
+          <t>277080</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>287298</t>
+          <t>287320</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -13291,12 +13291,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13306,12 +13306,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>998</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5861</t>
+          <t>5844</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>981</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5509</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13376,7 +13376,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -13404,12 +13404,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7711</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18793</t>
+          <t>18493</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7895</t>
+          <t>7972</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19005</t>
+          <t>19374</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -13517,12 +13517,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2358</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>299619</t>
+          <t>300111</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>311434</t>
+          <t>311862</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>302495</t>
+          <t>302533</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>314952</t>
+          <t>315027</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,97%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>704</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5732</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3643</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>12284</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5359</t>
+          <t>5522</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14934</t>
+          <t>14823</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4848</t>
+          <t>4943</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14642</t>
+          <t>14543</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12172</t>
+          <t>12219</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>33671</t>
+          <t>33712</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>21751</t>
+          <t>20686</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>44028</t>
+          <t>43095</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>620889</t>
+          <t>620528</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>631108</t>
+          <t>631190</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>975107</t>
+          <t>975743</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1002499</t>
+          <t>1002559</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,7 +14023,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1601928</t>
+          <t>1602487</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1628887</t>
+          <t>1629191</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5414-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5414-Clase-trans_orig.xlsx
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4765</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5422</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55061</t>
+          <t>55019</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>84071</t>
+          <t>84079</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>5430</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>6319</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>805</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7144</t>
+          <t>7344</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4282</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8666</t>
+          <t>9492</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64610</t>
+          <t>64410</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70935</t>
+          <t>70949</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17721</t>
+          <t>16824</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>85910</t>
+          <t>85118</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>94237</t>
+          <t>94222</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>5806</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6051</t>
+          <t>6406</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>881</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8354</t>
+          <t>8588</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>1801</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11782</t>
+          <t>10457</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>249010</t>
+          <t>249001</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>258129</t>
+          <t>258124</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>81045</t>
+          <t>80466</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>332337</t>
+          <t>333239</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>343022</t>
+          <t>343083</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>4611</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>8943</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>837</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>9083</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51016</t>
+          <t>50854</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>88963</t>
+          <t>87307</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>142392</t>
+          <t>142632</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>150883</t>
+          <t>150878</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2993,7 +2993,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>894</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9155</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>891</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9115</t>
+          <t>9051</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10682</t>
+          <t>10584</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10699</t>
+          <t>9656</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>409478</t>
+          <t>410079</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>421893</t>
+          <t>421878</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>413740</t>
+          <t>413558</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>425612</t>
+          <t>425729</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5668</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10434</t>
+          <t>10309</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2351</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13351</t>
+          <t>13032</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3731</t>
+          <t>3681</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15383</t>
+          <t>14056</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4264</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>15989</t>
+          <t>17290</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10154</t>
+          <t>10210</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>26577</t>
+          <t>26248</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>484198</t>
+          <t>485030</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>496196</t>
+          <t>496342</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>655807</t>
+          <t>654809</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>669677</t>
+          <t>669963</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1144301</t>
+          <t>1145856</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1163197</t>
+          <t>1164002</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>5530</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>5633</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20488</t>
+          <t>19759</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>63701</t>
+          <t>63574</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4683</t>
+          <t>5389</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6864</t>
+          <t>5725</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>5812</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8994</t>
+          <t>7846</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53766</t>
+          <t>54905</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12624</t>
+          <t>12078</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69103</t>
+          <t>70887</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78471</t>
+          <t>78483</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5899</t>
+          <t>5018</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6756</t>
+          <t>7403</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7208</t>
+          <t>7159</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>110119</t>
+          <t>109540</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>117712</t>
+          <t>117718</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>164759</t>
+          <t>164694</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>172342</t>
+          <t>172317</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8432</t>
+          <t>8514</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>975</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>8413</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4265</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20510</t>
+          <t>19399</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4224</t>
+          <t>4276</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19255</t>
+          <t>19345</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>208900</t>
+          <t>208346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>225333</t>
+          <t>225211</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>268659</t>
+          <t>269252</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>285605</t>
+          <t>285425</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2070</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12677</t>
+          <t>12304</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14977</t>
+          <t>14870</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>5063</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2978</t>
+          <t>2253</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12771</t>
+          <t>13089</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>14150</t>
+          <t>15011</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>93404</t>
+          <t>94474</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>101696</t>
+          <t>101704</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>167497</t>
+          <t>167822</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>181921</t>
+          <t>182054</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>267474</t>
+          <t>266380</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>282769</t>
+          <t>282815</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,16%</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2212</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13568</t>
+          <t>13081</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,47 +6489,47 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>6505</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>2253</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>12704</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
           <t>0,57%</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>6505</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>2188</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>13177</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6494</t>
+          <t>7004</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22855</t>
+          <t>22876</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,47 +6602,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>5,8%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>13025</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>6549</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>3,28%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>1,65%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>5,79%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>13025</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>6617</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>22982</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>364572</t>
+          <t>364675</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>383818</t>
+          <t>383173</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>366670</t>
+          <t>366375</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>385669</t>
+          <t>384780</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12518</t>
+          <t>12321</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7512</t>
+          <t>6751</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>22651</t>
+          <t>21382</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11830</t>
+          <t>12226</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>29776</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7390</t>
+          <t>7535</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24990</t>
+          <t>25538</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>13341</t>
+          <t>13232</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>33452</t>
+          <t>32784</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,47 +7058,47 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>4,42%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>35480</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>23472</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>50312</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>1,8%</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>35480</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>22931</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>48628</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>528178</t>
+          <t>527851</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>547452</t>
+          <t>547199</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>694868</t>
+          <t>694325</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>718729</t>
+          <t>718803</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1229841</t>
+          <t>1229070</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1261329</t>
+          <t>1260033</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,8%</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>6476</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>7046</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29458</t>
+          <t>30412</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>98647</t>
+          <t>98489</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5075</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4657</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5962</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47274</t>
+          <t>47153</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64173</t>
+          <t>64250</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -8615,7 +8615,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t>3954</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -8723,7 +8723,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>116936</t>
+          <t>116403</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8793,7 +8793,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>161904</t>
+          <t>162516</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>836</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9275</t>
+          <t>8656</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10084</t>
+          <t>9136</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9121,7 +9121,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2566</t>
+          <t>2507</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14116</t>
+          <t>13658</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>194581</t>
+          <t>195200</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>202980</t>
+          <t>203020</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>88962</t>
+          <t>89910</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>288786</t>
+          <t>289244</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>300336</t>
+          <t>300395</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6706</t>
+          <t>6785</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>823</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8734</t>
+          <t>8581</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9542,7 +9542,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2553</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14557</t>
+          <t>12858</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4846</t>
+          <t>4705</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>17998</t>
+          <t>17867</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>136487</t>
+          <t>136640</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>144392</t>
+          <t>144398</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>143493</t>
+          <t>144093</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>156884</t>
+          <t>156790</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>284268</t>
+          <t>284986</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>298951</t>
+          <t>299248</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3233</t>
+          <t>2470</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17052</t>
+          <t>16612</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3233</t>
+          <t>2470</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17052</t>
+          <t>16612</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5117</t>
+          <t>5145</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20354</t>
+          <t>21278</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5117</t>
+          <t>5145</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20354</t>
+          <t>21278</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>382028</t>
+          <t>382729</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>401959</t>
+          <t>402071</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>382028</t>
+          <t>382729</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>401959</t>
+          <t>402071</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -10326,7 +10326,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4480</t>
+          <t>3810</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18066</t>
+          <t>18526</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4609</t>
+          <t>4540</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>19546</t>
+          <t>19323</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4367</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15930</t>
+          <t>15665</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>13102</t>
+          <t>13430</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>34090</t>
+          <t>33910</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>20519</t>
+          <t>20077</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>42915</t>
+          <t>44530</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>574837</t>
+          <t>574420</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>586254</t>
+          <t>586161</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>727984</t>
+          <t>726319</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>752320</t>
+          <t>752120</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1306518</t>
+          <t>1307015</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1334642</t>
+          <t>1335394</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,92%</t>
         </is>
       </c>
     </row>
@@ -11232,7 +11232,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -11267,7 +11267,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -11345,17 +11345,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11380,17 +11380,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11415,17 +11415,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11497,7 +11497,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>657</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -11507,12 +11507,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11532,7 +11532,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>657</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -11542,12 +11542,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2863</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -11575,7 +11575,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>601</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -11585,12 +11585,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3568</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -11600,7 +11600,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11645,7 +11645,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>601</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -11655,12 +11655,12 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>3020</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -11688,27 +11688,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>94381</t>
+          <t>104114</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91430</t>
+          <t>100629</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -11723,27 +11723,27 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>46356</t>
+          <t>54728</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43972</t>
+          <t>52149</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -11758,27 +11758,27 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>140737</t>
+          <t>158842</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>138396</t>
+          <t>156189</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -11801,17 +11801,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11836,17 +11836,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11871,17 +11871,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11918,7 +11918,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>820</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -11928,12 +11928,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11988,7 +11988,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>820</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -11998,12 +11998,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>2726</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -12013,7 +12013,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -12031,32 +12031,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>483</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5661</t>
+          <t>5962</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12066,7 +12066,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -12076,12 +12076,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>995</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7025</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -12144,32 +12144,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>99215</t>
+          <t>109659</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>95376</t>
+          <t>105821</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>101093</t>
+          <t>111614</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12179,27 +12179,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>51812</t>
+          <t>56790</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49255</t>
+          <t>52765</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>151028</t>
+          <t>166450</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>146865</t>
+          <t>162381</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>153149</t>
+          <t>168863</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -12257,17 +12257,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12292,17 +12292,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>342</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -12384,12 +12384,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12409,32 +12409,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>312</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4399</t>
+          <t>3474</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12444,32 +12444,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1487</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>418</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -12487,32 +12487,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4980</t>
+          <t>4994</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9408</t>
+          <t>9283</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12522,32 +12522,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>1491</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>335</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5586</t>
+          <t>4184</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12557,32 +12557,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>6485</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>3518</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12880</t>
+          <t>11573</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -12600,32 +12600,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>232876</t>
+          <t>254670</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>228509</t>
+          <t>250524</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>236012</t>
+          <t>257681</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12635,32 +12635,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>324049</t>
+          <t>128239</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>317607</t>
+          <t>125339</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>326502</t>
+          <t>130113</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12670,32 +12670,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>556925</t>
+          <t>382909</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>549507</t>
+          <t>377619</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>562446</t>
+          <t>386341</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -12713,17 +12713,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>238197</t>
+          <t>260006</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>238197</t>
+          <t>260006</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>238197</t>
+          <t>260006</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12748,17 +12748,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12783,17 +12783,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>564890</t>
+          <t>390886</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>564890</t>
+          <t>390886</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>564890</t>
+          <t>390886</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12830,7 +12830,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>951</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -12840,12 +12840,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3701</t>
+          <t>3156</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12865,32 +12865,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1628</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6509</t>
+          <t>7193</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12900,32 +12900,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>4208</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7673</t>
+          <t>8587</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -12943,32 +12943,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>388</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12978,32 +12978,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8759</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5653</t>
+          <t>5665</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14074</t>
+          <t>14011</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13013,32 +13013,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>10195</t>
+          <t>10540</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6777</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>15479</t>
+          <t>16069</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -13056,32 +13056,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>89594</t>
+          <t>98414</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>86240</t>
+          <t>95422</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>91172</t>
+          <t>100027</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13091,32 +13091,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>193143</t>
+          <t>207661</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>187627</t>
+          <t>201743</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>197182</t>
+          <t>211676</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13126,32 +13126,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>282737</t>
+          <t>306075</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>277080</t>
+          <t>299249</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>287320</t>
+          <t>310745</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -13169,17 +13169,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13204,17 +13204,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>205133</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>205133</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>205133</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13239,17 +13239,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>297139</t>
+          <t>321037</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>297139</t>
+          <t>321037</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>297139</t>
+          <t>321037</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -13321,67 +13321,67 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5844</t>
+          <t>6303</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>2859</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>1198</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>6400</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
           <t>0,82%</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>2625</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>981</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>5534</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -13434,32 +13434,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>12336</t>
+          <t>13804</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7551</t>
+          <t>8656</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18493</t>
+          <t>21278</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13469,32 +13469,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>12336</t>
+          <t>13804</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7972</t>
+          <t>8434</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19374</t>
+          <t>21498</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -13512,7 +13512,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -13547,32 +13547,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>306711</t>
+          <t>329121</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>300111</t>
+          <t>321175</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>311862</t>
+          <t>334719</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13582,32 +13582,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>309915</t>
+          <t>332397</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>302533</t>
+          <t>323763</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>315027</t>
+          <t>337958</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -13625,17 +13625,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13660,17 +13660,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>321672</t>
+          <t>345783</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>321672</t>
+          <t>345783</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>321672</t>
+          <t>345783</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13695,17 +13695,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13742,32 +13742,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>823</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4851</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13777,32 +13777,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>7576</t>
+          <t>8137</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12284</t>
+          <t>13196</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13812,32 +13812,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>9723</t>
+          <t>10251</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>6525</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14823</t>
+          <t>15738</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -13855,32 +13855,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>9057</t>
+          <t>9015</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4943</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14543</t>
+          <t>15261</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13890,32 +13890,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>23569</t>
+          <t>25585</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12219</t>
+          <t>18612</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>33712</t>
+          <t>34082</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13925,32 +13925,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>32626</t>
+          <t>34601</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>20686</t>
+          <t>26316</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>43095</t>
+          <t>44382</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -13968,32 +13968,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>626849</t>
+          <t>690534</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>620528</t>
+          <t>684209</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>631190</t>
+          <t>694445</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14003,32 +14003,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>987394</t>
+          <t>851099</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>975743</t>
+          <t>841978</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1002559</t>
+          <t>859137</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14038,32 +14038,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1614243</t>
+          <t>1541633</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1602487</t>
+          <t>1531909</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1629191</t>
+          <t>1551224</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -14081,17 +14081,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>638053</t>
+          <t>701663</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>638053</t>
+          <t>701663</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>638053</t>
+          <t>701663</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14116,17 +14116,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1018539</t>
+          <t>884821</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1018539</t>
+          <t>884821</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1018539</t>
+          <t>884821</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14151,17 +14151,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1656592</t>
+          <t>1586484</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1656592</t>
+          <t>1586484</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1656592</t>
+          <t>1586484</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
